--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0002T0006Z000C1N59_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0002T0006Z000C1N59_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>47.07120626456676</v>
+        <v>7.649071017992099</v>
       </c>
       <c r="D2" t="n">
-        <v>47.4288538526684</v>
+        <v>7.707188751058615</v>
       </c>
       <c r="E2" t="n">
-        <v>8.111128296411882</v>
+        <v>1.318058348166931</v>
       </c>
       <c r="F2" t="n">
-        <v>7.84620247097547</v>
+        <v>1.275007901533514</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>61.89587032831124</v>
+        <v>10.05807892835058</v>
       </c>
       <c r="D3" t="n">
-        <v>64.26372899901378</v>
+        <v>10.44285596233974</v>
       </c>
       <c r="E3" t="n">
-        <v>8.111128296411882</v>
+        <v>1.318058348166931</v>
       </c>
       <c r="F3" t="n">
-        <v>7.84620247097547</v>
+        <v>1.275007901533514</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>48.27066686885503</v>
+        <v>7.843983366188943</v>
       </c>
       <c r="D4" t="n">
-        <v>50.4370579955087</v>
+        <v>8.196021924270163</v>
       </c>
       <c r="E4" t="n">
-        <v>8.111128296411882</v>
+        <v>1.318058348166931</v>
       </c>
       <c r="F4" t="n">
-        <v>7.84620247097547</v>
+        <v>1.275007901533514</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>50.32210407666079</v>
+        <v>8.177341912457379</v>
       </c>
       <c r="D5" t="n">
-        <v>48.20433268069512</v>
+        <v>7.833204060612958</v>
       </c>
       <c r="E5" t="n">
-        <v>8.111128296411882</v>
+        <v>1.318058348166931</v>
       </c>
       <c r="F5" t="n">
-        <v>7.84620247097547</v>
+        <v>1.275007901533514</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>67.30326487170271</v>
+        <v>10.93678054165169</v>
       </c>
       <c r="D6" t="n">
-        <v>64.88349439900233</v>
+        <v>10.54356783983788</v>
       </c>
       <c r="E6" t="n">
-        <v>8.111128296411882</v>
+        <v>1.318058348166931</v>
       </c>
       <c r="F6" t="n">
-        <v>7.84620247097547</v>
+        <v>1.275007901533514</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
